--- a/data/trans_dic/P04D$aparatos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 52,22</t>
+          <t>42,61; 52,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,43; 52,18</t>
+          <t>42,38; 52,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,5; 56,41</t>
+          <t>47,72; 56,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,4; 54,57</t>
+          <t>42,57; 54,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,29; 47,34</t>
+          <t>36,4; 47,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,54; 54,22</t>
+          <t>46,57; 54,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,73; 51,89</t>
+          <t>43,8; 51,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,85; 48,27</t>
+          <t>40,74; 48,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,09; 54,22</t>
+          <t>48,1; 54,41</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,4; 60,13</t>
+          <t>49,72; 60,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,44; 56,92</t>
+          <t>46,43; 57,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,02; 64,12</t>
+          <t>54,12; 64,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,25; 62,62</t>
+          <t>51,2; 63,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,91; 54,88</t>
+          <t>43,97; 54,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,49; 61,21</t>
+          <t>52,16; 60,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,06; 59,64</t>
+          <t>51,81; 59,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 54,32</t>
+          <t>46,44; 54,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,45; 61,17</t>
+          <t>54,69; 61,34</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,83; 67,92</t>
+          <t>59,69; 67,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,39; 57,25</t>
+          <t>48,68; 57,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 66,96</t>
+          <t>16,75; 67,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,94; 68,14</t>
+          <t>55,95; 68,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,1; 63,26</t>
+          <t>47,77; 62,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,79; 69,99</t>
+          <t>56,99; 70,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,45; 66,84</t>
+          <t>60,53; 66,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,55; 57,05</t>
+          <t>49,74; 57,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,19; 66,09</t>
+          <t>17,47; 66,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 71,72</t>
+          <t>65,82; 71,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,48; 57,5</t>
+          <t>51,53; 57,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,35; 71,98</t>
+          <t>65,3; 71,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,73; 67,81</t>
+          <t>60,79; 67,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,42; 56,04</t>
+          <t>49,3; 56,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,91; 84,29</t>
+          <t>63,95; 86,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,69; 69,1</t>
+          <t>64,71; 69,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,6; 56,03</t>
+          <t>51,6; 56,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,41; 79,75</t>
+          <t>66,47; 79,77</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,46; 78,28</t>
+          <t>70,49; 78,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,81; 62,15</t>
+          <t>54,31; 62,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,03; 74,96</t>
+          <t>66,05; 75,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,94; 73,94</t>
+          <t>67,49; 73,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,87; 63,21</t>
+          <t>55,95; 63,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,14; 75,63</t>
+          <t>51,09; 76,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,71; 74,8</t>
+          <t>69,58; 74,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,17; 61,61</t>
+          <t>55,93; 61,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,89; 74,1</t>
+          <t>57,24; 74,06</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49,27; 61,28</t>
+          <t>48,92; 61,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,48; 53,75</t>
+          <t>41,99; 53,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,85; 73,54</t>
+          <t>51,92; 73,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,38; 71,98</t>
+          <t>66,4; 71,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,99; 54,29</t>
+          <t>47,87; 54,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,5; 74,86</t>
+          <t>68,62; 74,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,08</t>
+          <t>64,1; 69,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,06; 52,64</t>
+          <t>47,33; 52,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,83; 73,04</t>
+          <t>65,95; 73,31</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,61; 64,95</t>
+          <t>61,48; 65,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,36; 54,77</t>
+          <t>51,37; 54,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,2; 64,8</t>
+          <t>46,3; 64,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,31; 66,64</t>
+          <t>63,24; 66,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,57; 53,97</t>
+          <t>50,31; 53,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,89; 71,92</t>
+          <t>62,62; 71,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,9; 65,27</t>
+          <t>62,93; 65,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,4; 53,79</t>
+          <t>51,57; 54,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,14; 66,45</t>
+          <t>55,89; 66,49</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>183860; 228302</t>
+          <t>186281; 228025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>182066; 223884</t>
+          <t>181858; 224064</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239475; 284416</t>
+          <t>240592; 285426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>133337; 171584</t>
+          <t>133858; 170549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>125950; 164296</t>
+          <t>126328; 163546</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>203147; 241868</t>
+          <t>207751; 243222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>328692; 390056</t>
+          <t>329236; 385979</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>317020; 374656</t>
+          <t>316165; 375258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>457041; 515287</t>
+          <t>457136; 517099</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>205690; 250390</t>
+          <t>207030; 251171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175195; 214734</t>
+          <t>175130; 215223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244280; 289974</t>
+          <t>244727; 289687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173231; 211663</t>
+          <t>173047; 213552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163452; 204320</t>
+          <t>163684; 202681</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>200809; 234175</t>
+          <t>199571; 232643</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>392760; 449928</t>
+          <t>390865; 450334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>349614; 407157</t>
+          <t>348097; 407641</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>454570; 510670</t>
+          <t>456587; 512023</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>376608; 427503</t>
+          <t>375716; 426901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>252560; 298797</t>
+          <t>254078; 297976</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111032; 446827</t>
+          <t>111772; 448088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145528; 177262</t>
+          <t>145548; 178602</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78243; 105093</t>
+          <t>79359; 104649</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95496; 115642</t>
+          <t>94172; 115896</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>537738; 594545</t>
+          <t>538441; 595291</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>340907; 392496</t>
+          <t>342223; 396071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159767; 550242</t>
+          <t>145462; 551006</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>761371; 829937</t>
+          <t>761599; 825677</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>591794; 661057</t>
+          <t>592425; 661613</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>674273; 742748</t>
+          <t>673743; 740061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>465027; 519223</t>
+          <t>465444; 518392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>408167; 462780</t>
+          <t>407194; 463337</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624204; 823241</t>
+          <t>624595; 846637</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1243840; 1328682</t>
+          <t>1244207; 1329423</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1019458; 1106854</t>
+          <t>1019416; 1107084</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1333901; 1601734</t>
+          <t>1335083; 1602118</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>358410; 398164</t>
+          <t>358543; 398512</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>333984; 385785</t>
+          <t>337098; 386119</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313002; 355329</t>
+          <t>313065; 357248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>509043; 562203</t>
+          <t>513207; 560835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>412481; 466655</t>
+          <t>413078; 468089</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>404102; 634867</t>
+          <t>428828; 638426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>884721; 949284</t>
+          <t>882988; 950348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>763295; 837260</t>
+          <t>760080; 834210</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747246; 973222</t>
+          <t>751762; 972752</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>131060; 163014</t>
+          <t>130148; 164138</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119118; 154343</t>
+          <t>120583; 152448</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>124710; 176859</t>
+          <t>124871; 176736</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>734971; 796952</t>
+          <t>735245; 797027</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>519250; 587403</t>
+          <t>517914; 585633</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>520471; 568833</t>
+          <t>521401; 569563</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>881314; 948677</t>
+          <t>880220; 952814</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>644376; 720690</t>
+          <t>648061; 724041</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658568; 730655</t>
+          <t>659734; 733319</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2103978; 2217758</t>
+          <t>2099301; 2220127</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1738953; 1854354</t>
+          <t>1739278; 1852156</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1557003; 2183686</t>
+          <t>1560358; 2185806</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2244861; 2363020</t>
+          <t>2242538; 2360867</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1785900; 1905994</t>
+          <t>1776769; 1904468</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2245111; 2567345</t>
+          <t>2235527; 2568334</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4378247; 4543143</t>
+          <t>4380377; 4555235</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3555272; 3720990</t>
+          <t>3566976; 3738352</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3826395; 4611785</t>
+          <t>3878975; 4614320</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$aparatos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,61; 52,15</t>
+          <t>41,9; 51,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,38; 52,22</t>
+          <t>42,39; 52,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,72; 56,61</t>
+          <t>47,63; 56,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,57; 54,24</t>
+          <t>42,8; 54,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,4; 47,12</t>
+          <t>36,43; 46,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,57; 54,52</t>
+          <t>46,52; 54,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,8; 51,35</t>
+          <t>43,72; 51,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,74; 48,35</t>
+          <t>41,09; 48,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,1; 54,41</t>
+          <t>48,55; 54,15</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,72; 60,32</t>
+          <t>49,62; 59,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,43; 57,05</t>
+          <t>46,42; 57,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,12; 64,06</t>
+          <t>54,7; 64,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,2; 63,18</t>
+          <t>51,06; 62,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,97; 54,44</t>
+          <t>43,6; 54,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,16; 60,81</t>
+          <t>52,23; 60,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,81; 59,69</t>
+          <t>51,88; 59,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,44; 54,39</t>
+          <t>46,69; 53,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,69; 61,34</t>
+          <t>54,82; 61,53</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,69; 67,83</t>
+          <t>59,98; 67,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,68; 57,09</t>
+          <t>48,27; 57,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,75; 67,15</t>
+          <t>61,12; 70,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,95; 68,66</t>
+          <t>56,28; 68,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,77; 62,99</t>
+          <t>47,39; 62,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,99; 70,14</t>
+          <t>56,65; 69,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,53; 66,92</t>
+          <t>60,14; 66,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,74; 57,57</t>
+          <t>49,97; 57,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 66,18</t>
+          <t>61,51; 68,83</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,82; 71,36</t>
+          <t>66,12; 71,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,53; 57,55</t>
+          <t>51,65; 57,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,72</t>
+          <t>64,41; 70,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,79; 67,7</t>
+          <t>60,18; 67,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 56,1</t>
+          <t>49,37; 56,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,95; 86,68</t>
+          <t>60,93; 66,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,71; 69,14</t>
+          <t>64,72; 68,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,6; 56,04</t>
+          <t>51,44; 56,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,47; 79,77</t>
+          <t>63,97; 67,98</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,49; 78,34</t>
+          <t>70,91; 78,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,31; 62,21</t>
+          <t>54,01; 62,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,05; 75,37</t>
+          <t>64,42; 72,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,49; 73,76</t>
+          <t>67,28; 73,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,95; 63,41</t>
+          <t>55,97; 63,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,09; 76,06</t>
+          <t>70,67; 75,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,58; 74,89</t>
+          <t>69,53; 74,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>55,93; 61,39</t>
+          <t>56,23; 61,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,24; 74,06</t>
+          <t>69,01; 73,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,92; 61,7</t>
+          <t>48,7; 61,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,99; 53,09</t>
+          <t>41,61; 53,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,92; 73,48</t>
+          <t>56,62; 76,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,4; 71,98</t>
+          <t>66,55; 72,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,87; 54,12</t>
+          <t>47,8; 54,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,62; 74,96</t>
+          <t>69,06; 75,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,1; 69,38</t>
+          <t>64,09; 69,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,33; 52,88</t>
+          <t>47,38; 52,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,95; 73,31</t>
+          <t>67,66; 74,16</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,48; 65,01</t>
+          <t>61,49; 64,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,37; 54,7</t>
+          <t>51,24; 54,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,3; 64,86</t>
+          <t>61,93; 65,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,24; 66,58</t>
+          <t>63,52; 66,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,31; 53,93</t>
+          <t>50,43; 53,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,62; 71,95</t>
+          <t>63,65; 66,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,93; 65,44</t>
+          <t>63,0; 65,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,57; 54,04</t>
+          <t>51,43; 53,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,89; 66,49</t>
+          <t>63,43; 65,66</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>245328</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>487001</t>
+          <t>531540</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>186281; 228025</t>
+          <t>183203; 225820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>181858; 224064</t>
+          <t>181901; 223596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>240592; 285426</t>
+          <t>261692; 310661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>133858; 170549</t>
+          <t>134581; 172848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>126328; 163546</t>
+          <t>126422; 162339</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>207751; 243222</t>
+          <t>226535; 264812</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>329236; 385979</t>
+          <t>328617; 385627</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>316165; 375258</t>
+          <t>318946; 372794</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>457136; 517099</t>
+          <t>503194; 561221</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268235</t>
+          <t>289292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>238660</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>485762</t>
+          <t>527951</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>207030; 251171</t>
+          <t>206627; 249224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175130; 215223</t>
+          <t>175113; 215042</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244727; 289687</t>
+          <t>264309; 310187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173047; 213552</t>
+          <t>172574; 211745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163684; 202681</t>
+          <t>162329; 202575</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>199571; 232643</t>
+          <t>221016; 256170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>390865; 450334</t>
+          <t>391410; 448072</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>348097; 407641</t>
+          <t>349978; 404249</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>456587; 512023</t>
+          <t>496888; 557636</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277952</t>
+          <t>310575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>105583</t>
+          <t>117289</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>383535</t>
+          <t>427864</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>375716; 426901</t>
+          <t>377536; 426304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>254078; 297976</t>
+          <t>251907; 300149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111772; 448088</t>
+          <t>287671; 330854</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145548; 178602</t>
+          <t>146403; 178859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79359; 104649</t>
+          <t>78733; 104601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94172; 115896</t>
+          <t>105246; 128623</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>538441; 595291</t>
+          <t>535000; 592893</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>342223; 396071</t>
+          <t>343838; 398244</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145462; 551006</t>
+          <t>403762; 451821</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709875</t>
+          <t>760465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>705294</t>
+          <t>547976</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1415170</t>
+          <t>1308442</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>761599; 825677</t>
+          <t>765043; 827451</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>592425; 661613</t>
+          <t>593831; 662848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>673743; 740061</t>
+          <t>724929; 794016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>465444; 518392</t>
+          <t>460795; 515432</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>407194; 463337</t>
+          <t>407744; 466558</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624595; 846637</t>
+          <t>523343; 572097</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1244207; 1329423</t>
+          <t>1244446; 1324818</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1019416; 1107084</t>
+          <t>1016249; 1106690</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1335083; 1602118</t>
+          <t>1269345; 1348968</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334922</t>
+          <t>388357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>575198</t>
+          <t>606898</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>910121</t>
+          <t>995255</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>358543; 398512</t>
+          <t>360721; 398950</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>337098; 386119</t>
+          <t>335267; 385309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313065; 357248</t>
+          <t>365170; 411927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>513207; 560835</t>
+          <t>511604; 561248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>413078; 468089</t>
+          <t>413170; 466721</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>428828; 638426</t>
+          <t>585714; 628550</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>882988; 950348</t>
+          <t>882395; 948940</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>760080; 834210</t>
+          <t>764128; 837388</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>751762; 972752</t>
+          <t>963146; 1027296</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152206</t>
+          <t>158417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>546493</t>
+          <t>606664</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>698699</t>
+          <t>765082</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>130148; 164138</t>
+          <t>129542; 163205</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120583; 152448</t>
+          <t>119492; 154043</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>124871; 176736</t>
+          <t>134324; 181413</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>735245; 797027</t>
+          <t>736833; 799703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>517914; 585633</t>
+          <t>517183; 585014</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>521401; 569563</t>
+          <t>581823; 632630</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>880220; 952814</t>
+          <t>880153; 948790</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>648061; 724041</t>
+          <t>648676; 723921</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659734; 733319</t>
+          <t>730492; 800636</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2005606</t>
+          <t>2193318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2374681</t>
+          <t>2362815</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4380288</t>
+          <t>4556133</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2099301; 2220127</t>
+          <t>2099752; 2216449</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1739278; 1852156</t>
+          <t>1734941; 1858964</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1560358; 2185806</t>
+          <t>2126123; 2248415</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2242538; 2360867</t>
+          <t>2252192; 2363411</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1776769; 1904468</t>
+          <t>1780863; 1902977</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2235527; 2568334</t>
+          <t>2307917; 2411357</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4380377; 4555235</t>
+          <t>4385582; 4546687</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3566976; 3738352</t>
+          <t>3557302; 3731450</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3878975; 4614320</t>
+          <t>4477450; 4635134</t>
         </is>
       </c>
     </row>
